--- a/category・term関数.xlsx
+++ b/category・term関数.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\50_knowledge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE1EF716-2EDF-4D45-973A-3B57B9A3E3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E538C6-5736-40FB-862D-C821833579E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{86D971F8-5C6D-4AF2-9815-A337DF71804B}"/>
   </bookViews>
@@ -284,6 +284,94 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>103837</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>161726</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3E1987B-F2CB-9511-FB4C-98C4DB212E69}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12487275" y="2143125"/>
+          <a:ext cx="7504762" cy="1590476"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>256562</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>238082</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBEC3A02-CC33-151A-3731-EA8E63CD3D82}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12496800" y="1800225"/>
+          <a:ext cx="4904762" cy="342857"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
